--- a/data/trans_camb/P16A12-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Edad-trans_camb.xlsx
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,06</t>
+          <t>-0,38; 1,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,68</t>
+          <t>-0,4; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,0</t>
+          <t>-0,99; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,12</t>
+          <t>0,23; 1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,13</t>
+          <t>0,02; 1,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,34</t>
+          <t>-0,2; 0,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,63</t>
+          <t>-0,2; 0,6</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,67</t>
+          <t>0,32; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,91</t>
+          <t>-0,49; 1,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,05</t>
+          <t>-0,01; 2,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,84</t>
+          <t>-0,5; 0,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,28</t>
+          <t>-0,92; 0,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,04</t>
+          <t>0,49; 2,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,66</t>
+          <t>-0,37; 0,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,74</t>
+          <t>-0,46; 0,7</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,17; —</t>
+          <t>-50,48; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,6; 2050,91</t>
+          <t>17,24; 2164,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 1054,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,16</t>
+          <t>-2,44; -0,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,74</t>
+          <t>-1,77; 0,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,67</t>
+          <t>-1,25; 1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,01</t>
+          <t>-0,33; 2,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,34</t>
+          <t>-0,78; 1,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,03</t>
+          <t>-0,88; 1,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,68</t>
+          <t>-1,04; 0,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,73</t>
+          <t>-0,91; 0,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,01</t>
+          <t>-0,77; 0,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,58; -1,66</t>
+          <t>-92,89; 8,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,12; 72,4</t>
+          <t>-71,01; 82,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 152,45</t>
+          <t>-52,85; 155,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 476,47</t>
+          <t>-32,93; 458,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 388,32</t>
+          <t>-59,34; 352,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 280,95</t>
+          <t>-69,54; 242,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 81,03</t>
+          <t>-56,47; 77,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 84,89</t>
+          <t>-55,57; 86,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 111,79</t>
+          <t>-46,73; 102,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,42</t>
+          <t>-3,57; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,58</t>
+          <t>-1,38; 3,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,05</t>
+          <t>-4,02; 3,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,37</t>
+          <t>-1,98; 2,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,96</t>
+          <t>-2,21; 1,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,15</t>
+          <t>-2,7; 1,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,16</t>
+          <t>-1,96; 1,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,04</t>
+          <t>-1,34; 2,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,45</t>
+          <t>-2,01; 1,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,47; 48,01</t>
+          <t>-60,0; 47,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 115,01</t>
+          <t>-25,57; 115,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,31; 81,51</t>
+          <t>-65,74; 91,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 111,43</t>
+          <t>-46,21; 105,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 86,77</t>
+          <t>-48,28; 82,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 58,4</t>
+          <t>-54,2; 58,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 39,38</t>
+          <t>-40,87; 46,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 65,19</t>
+          <t>-28,52; 68,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 42,7</t>
+          <t>-43,2; 48,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,61</t>
+          <t>-4,79; 4,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 4,85</t>
+          <t>-4,35; 4,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,13</t>
+          <t>-3,84; 4,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,81</t>
+          <t>-2,74; 5,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,6</t>
+          <t>-2,5; 5,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,38</t>
+          <t>-7,33; -0,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,63</t>
+          <t>-2,78; 3,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,58</t>
+          <t>-2,31; 4,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,15</t>
+          <t>-3,96; 1,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 47,21</t>
+          <t>-33,03; 43,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 49,49</t>
+          <t>-30,01; 50,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 41,66</t>
+          <t>-27,33; 48,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 70,94</t>
+          <t>-22,52; 70,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 69,52</t>
+          <t>-20,75; 74,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,95; -4,29</t>
+          <t>-54,42; -7,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 38,54</t>
+          <t>-21,46; 39,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 46,92</t>
+          <t>-18,07; 42,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 12,85</t>
+          <t>-30,53; 12,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,44</t>
+          <t>2,84; 17,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,52; 14,41</t>
+          <t>1,5; 14,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 6,79</t>
+          <t>-4,25; 6,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 9,15</t>
+          <t>-3,07; 9,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 8,4</t>
+          <t>-4,25; 7,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -3,22</t>
+          <t>-19,68; -3,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,33</t>
+          <t>1,63; 10,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 8,47</t>
+          <t>0,03; 9,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -0,49</t>
+          <t>-13,87; -0,41</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,07; 102,44</t>
+          <t>12,44; 103,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,78; 88,22</t>
+          <t>6,42; 85,27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 41,52</t>
+          <t>-18,71; 42,31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 50,73</t>
+          <t>-12,81; 52,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 47,19</t>
+          <t>-18,89; 41,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,99; -15,77</t>
+          <t>-78,57; -15,93</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,95; 62,31</t>
+          <t>7,1; 60,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 47,27</t>
+          <t>-0,07; 50,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,33; -2,88</t>
+          <t>-59,7; -2,18</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 17,35</t>
+          <t>0,82; 16,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,84; 20,22</t>
+          <t>5,61; 20,48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,19; 14,59</t>
+          <t>1,46; 15,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,11; 16,35</t>
+          <t>3,72; 16,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 13,45</t>
+          <t>-0,03; 13,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,9; 14,3</t>
+          <t>3,29; 14,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,57; 15,21</t>
+          <t>4,51; 15,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,13</t>
+          <t>4,06; 14,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,03</t>
+          <t>4,04; 13,15</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2,7; 108,23</t>
+          <t>2,7; 103,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>22,18; 123,69</t>
+          <t>22,79; 125,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4,29; 87,99</t>
+          <t>6,07; 97,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,82; 95,83</t>
+          <t>15,15; 100,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 80,85</t>
+          <t>-1,36; 76,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,41; 84,89</t>
+          <t>13,21; 89,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,15; 85,33</t>
+          <t>18,4; 86,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16,45; 78,93</t>
+          <t>16,46; 81,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,44; 73,85</t>
+          <t>16,99; 77,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,9</t>
+          <t>0,52; 2,91</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,99</t>
+          <t>1,56; 4,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,9</t>
+          <t>0,61; 3,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,71</t>
+          <t>1,17; 3,68</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,96</t>
+          <t>0,56; 3,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,9</t>
+          <t>-0,46; 1,98</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,96</t>
+          <t>1,19; 2,92</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,17</t>
+          <t>1,31; 3,14</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,69</t>
+          <t>0,56; 2,57</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>9,13; 56,54</t>
+          <t>9,37; 59,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24,88; 78,04</t>
+          <t>23,78; 77,83</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14,5; 75,76</t>
+          <t>10,52; 74,64</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,73; 65,63</t>
+          <t>17,62; 68,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,44; 53,84</t>
+          <t>8,55; 55,36</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 33,87</t>
+          <t>-6,91; 35,7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,82; 53,44</t>
+          <t>19,2; 53,92</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>22,72; 58,32</t>
+          <t>21,18; 57,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9,74; 48,69</t>
+          <t>9,32; 47,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A12-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,08</t>
+          <t>-0,39; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,7</t>
+          <t>-0,4; 0,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,87</t>
+          <t>0,23; 1,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,15</t>
+          <t>0,02; 1,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,36</t>
+          <t>-0,2; 0,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,6</t>
+          <t>-0,2; 0,48</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,62</t>
+          <t>0,28; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,69</t>
+          <t>-0,59; 0,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,79</t>
+          <t>-0,49; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,24</t>
+          <t>0,04; 2,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,98</t>
+          <t>-0,55; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,29</t>
+          <t>-0,86; 0,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,03</t>
+          <t>0,4; 1,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,61</t>
+          <t>-0,31; 0,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,7</t>
+          <t>-0,46; 0,66</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,78%</t>
+          <t>-52,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>-2,85%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,48; —</t>
+          <t>-50,82; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 2164,32</t>
+          <t>25,8; 2085,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1054,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,12</t>
+          <t>-2,44; -0,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,8</t>
+          <t>-1,83; 0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,75</t>
+          <t>-1,24; 1,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,01</t>
+          <t>-0,3; 2,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,29</t>
+          <t>-0,9; 1,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,0</t>
+          <t>-0,81; 1,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,66</t>
+          <t>-1,03; 0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,72</t>
+          <t>-0,94; 0,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,94</t>
+          <t>-0,69; 1,16</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-92,89; 8,37</t>
+          <t>-91,5; 15,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 82,63</t>
+          <t>-72,53; 87,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 155,35</t>
+          <t>-52,81; 179,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 458,34</t>
+          <t>-34,4; 482,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,34; 352,38</t>
+          <t>-66,91; 289,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 242,44</t>
+          <t>-57,58; 282,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 77,94</t>
+          <t>-59,39; 75,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 86,98</t>
+          <t>-54,77; 100,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 102,39</t>
+          <t>-41,4; 133,11</t>
         </is>
       </c>
     </row>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,15</t>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,51</t>
+          <t>-3,39; 1,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,66</t>
+          <t>-1,41; 3,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,16</t>
+          <t>-0,63; 4,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,34</t>
+          <t>-1,98; 2,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,7</t>
+          <t>-2,34; 1,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,14</t>
+          <t>-2,41; 1,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,3</t>
+          <t>-1,91; 1,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,17</t>
+          <t>-1,3; 2,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,65</t>
+          <t>-0,89; 2,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,66%</t>
+          <t>-12,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,98%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 47,99</t>
+          <t>-57,42; 50,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 115,12</t>
+          <t>-25,87; 123,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,74; 91,97</t>
+          <t>-11,04; 160,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 105,13</t>
+          <t>-46,11; 98,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,28; 82,71</t>
+          <t>-51,84; 93,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 58,5</t>
+          <t>-50,65; 56,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 46,86</t>
+          <t>-39,53; 43,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 68,94</t>
+          <t>-26,43; 73,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 48,95</t>
+          <t>-19,48; 74,11</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,42</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,17</t>
+          <t>-5,01; 3,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 4,91</t>
+          <t>-3,88; 5,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,8</t>
+          <t>-3,65; 4,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,6</t>
+          <t>-2,93; 5,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,81</t>
+          <t>-2,7; 5,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,6</t>
+          <t>-7,07; -0,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,83</t>
+          <t>-2,61; 3,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,05</t>
+          <t>-2,16; 4,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,22</t>
+          <t>-3,93; 1,1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-34,0%</t>
+          <t>-33,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-11,59%</t>
+          <t>-11,69%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 43,7</t>
+          <t>-35,81; 41,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 50,81</t>
+          <t>-27,75; 54,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 48,55</t>
+          <t>-25,4; 48,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 70,85</t>
+          <t>-25,51; 68,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 74,87</t>
+          <t>-21,7; 70,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,42; -7,48</t>
+          <t>-56,07; -2,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 39,82</t>
+          <t>-20,42; 38,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 42,1</t>
+          <t>-17,21; 46,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 12,71</t>
+          <t>-31,39; 10,7</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-10,15</t>
+          <t>-4,77</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,66</t>
+          <t>-2,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,84; 17,08</t>
+          <t>2,79; 16,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,41</t>
+          <t>0,79; 14,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,95</t>
+          <t>-5,67; 5,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 9,5</t>
+          <t>-2,8; 9,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 7,28</t>
+          <t>-4,6; 6,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -3,08</t>
+          <t>-9,25; -0,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,82</t>
+          <t>1,63; 10,71</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 9,11</t>
+          <t>0,08; 8,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -0,41</t>
+          <t>-6,03; 1,31</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-48,9%</t>
+          <t>-22,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-28,08%</t>
+          <t>-10,85%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,44; 103,77</t>
+          <t>12,07; 97,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,42; 85,27</t>
+          <t>2,87; 84,59</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 42,31</t>
+          <t>-24,55; 36,0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 52,49</t>
+          <t>-12,0; 50,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 41,2</t>
+          <t>-20,12; 37,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,57; -15,93</t>
+          <t>-38,41; -0,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,1; 60,03</t>
+          <t>7,1; 58,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 50,17</t>
+          <t>0,44; 48,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-59,7; -2,18</t>
+          <t>-26,13; 7,32</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>8,57</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 16,8</t>
+          <t>1,07; 16,75</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,61; 20,48</t>
+          <t>5,57; 20,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,46; 15,11</t>
+          <t>0,83; 14,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,72; 16,81</t>
+          <t>3,12; 17,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 13,05</t>
+          <t>-1,42; 12,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,29; 14,48</t>
+          <t>3,76; 14,51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,51; 15,17</t>
+          <t>4,22; 15,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,16</t>
+          <t>3,61; 13,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,15</t>
+          <t>4,36; 12,51</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2,7; 103,27</t>
+          <t>3,43; 104,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>22,79; 125,62</t>
+          <t>21,81; 130,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6,07; 97,42</t>
+          <t>3,96; 89,92</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,15; 100,87</t>
+          <t>12,91; 99,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 76,96</t>
+          <t>-6,12; 71,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,21; 89,22</t>
+          <t>14,11; 91,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,4; 86,13</t>
+          <t>18,95; 85,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16,46; 81,25</t>
+          <t>15,29; 79,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16,99; 77,96</t>
+          <t>19,3; 74,89</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>2,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,91</t>
+          <t>0,44; 2,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,02</t>
+          <t>1,48; 3,88</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,76</t>
+          <t>1,86; 4,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,68</t>
+          <t>1,2; 3,66</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,08</t>
+          <t>0,53; 3,17</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,98</t>
+          <t>0,25; 2,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,92</t>
+          <t>1,21; 2,92</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,14</t>
+          <t>1,42; 3,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,57</t>
+          <t>1,43; 2,99</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>9,37; 59,52</t>
+          <t>6,85; 56,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>23,78; 77,83</t>
+          <t>23,48; 77,15</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10,52; 74,64</t>
+          <t>30,14; 82,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,62; 68,76</t>
+          <t>17,89; 66,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,55; 55,36</t>
+          <t>7,87; 56,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 35,7</t>
+          <t>3,46; 41,26</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,2; 53,92</t>
+          <t>19,11; 53,55</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>21,18; 57,99</t>
+          <t>22,47; 57,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9,32; 47,17</t>
+          <t>22,88; 56,3</t>
         </is>
       </c>
     </row>
